--- a/results/Int Task Remove ACC 0.7/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.7/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.0325229138015539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01800855505163386</v>
+        <v>0.01801386854791441</v>
       </c>
       <c r="F3" t="n">
         <v>0.00535268242944498</v>
@@ -1169,13 +1169,13 @@
         <v>0.01786716023183283</v>
       </c>
       <c r="I3" t="n">
-        <v>9.274104107144579e-05</v>
+        <v>9.274104107144687e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0005652472598974441</v>
+        <v>-0.000570187971359894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001506204966628213</v>
+        <v>0.001501293375272614</v>
       </c>
       <c r="L3" t="n">
         <v>0.001511482011483095</v>
@@ -1196,7 +1196,7 @@
         <v>-0.0006556224753869578</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008234923370909473</v>
+        <v>0.008250895098906173</v>
       </c>
       <c r="S3" t="n">
         <v>0.3699460360485287</v>
@@ -1208,7 +1208,7 @@
         <v>0.2955925770670905</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001092046447882644</v>
+        <v>9.756160832368186e-05</v>
       </c>
       <c r="W3" t="n">
         <v>-0.001375441190812233</v>
@@ -1364,7 +1364,7 @@
         <v>0.01386617130990488</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01489252748261308</v>
+        <v>0.01488190049005198</v>
       </c>
       <c r="BW3" t="n">
         <v>0.004143028634262613</v>
@@ -1428,7 +1428,7 @@
         <v>0.04432252263381508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0388599572740207</v>
+        <v>0.03887022859327355</v>
       </c>
       <c r="F4" t="n">
         <v>0.009636261285635226</v>
@@ -1440,13 +1440,13 @@
         <v>0.03589617945077711</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001032628836081734</v>
+        <v>0.001032628836081735</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01896199123125539</v>
+        <v>0.01896775493572636</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0209490589954725</v>
+        <v>0.02095769527177661</v>
       </c>
       <c r="L4" t="n">
         <v>0.02095336996534219</v>
@@ -1467,7 +1467,7 @@
         <v>0.007429473990190879</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02870804621321209</v>
+        <v>0.02873960354748121</v>
       </c>
       <c r="S4" t="n">
         <v>0.1354181997512854</v>
@@ -1479,7 +1479,7 @@
         <v>0.1311969240473793</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001038278961966104</v>
+        <v>0.001021747655715795</v>
       </c>
       <c r="W4" t="n">
         <v>0.003882150871414032</v>
@@ -1635,7 +1635,7 @@
         <v>0.02450630409862015</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0354654783479262</v>
+        <v>0.03543335851185766</v>
       </c>
       <c r="BW4" t="n">
         <v>0.009909001883495675</v>
@@ -1717,7 +1717,7 @@
         <v>-0.02128247650635703</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03163064833005898</v>
+        <v>-0.03167976424361497</v>
       </c>
       <c r="L5" t="n">
         <v>-0.03163064833005898</v>
@@ -2021,7 +2021,7 @@
         <v>0.1830032112470195</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0006760718140662147</v>
+        <v>-0.000663720035410087</v>
       </c>
       <c r="W6" t="n">
         <v>-0.001345690659049131</v>
@@ -2253,7 +2253,7 @@
         <v>0.01851121913084048</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004422332780541549</v>
+        <v>0.0004422332780541604</v>
       </c>
       <c r="J7" t="n">
         <v>-0.003068735529443916</v>
@@ -2292,7 +2292,7 @@
         <v>0.3435275867193436</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000451647183846926</v>
+        <v>0.0003869541182973779</v>
       </c>
       <c r="W7" t="n">
         <v>-0.000316994845709978</v>
@@ -2563,7 +2563,7 @@
         <v>0.3843017619026936</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0009578279952313085</v>
+        <v>0.0009487151581884984</v>
       </c>
       <c r="W8" t="n">
         <v>0.000197889182058042</v>
@@ -2783,7 +2783,7 @@
         <v>0.08493083003952567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08560042507970239</v>
+        <v>0.08565356004250792</v>
       </c>
       <c r="F9" t="n">
         <v>0.02036144578313249</v>
@@ -2822,7 +2822,7 @@
         <v>0.008072289156626477</v>
       </c>
       <c r="R9" t="n">
-        <v>0.07242295430393193</v>
+        <v>0.07252922422954297</v>
       </c>
       <c r="S9" t="n">
         <v>0.6198193411264612</v>
@@ -2990,7 +2990,7 @@
         <v>0.053219989696033</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1113708820403825</v>
+        <v>0.1112646121147715</v>
       </c>
       <c r="BW9" t="n">
         <v>0.02812982998454407</v>
